--- a/openclaw_experiments/evolve_exp/claude_fp8_scratch_ten_5r/workflows/round_execution_times.xlsx
+++ b/openclaw_experiments/evolve_exp/claude_fp8_scratch_ten_5r/workflows/round_execution_times.xlsx
@@ -11,8 +11,8 @@
     <sheet name="题目耗时" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'轮次耗时'!$A$1:$H$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'题目耗时'!$A$1:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'轮次耗时'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'题目耗时'!$A$1:$I$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -796,8 +796,42 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>interaction_workflow_c83b67c63c37</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T16:07:23.053090</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T16:41:24.897463</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>2041.844373</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>34.03073955</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>derived_from_problem_artifact_intervals</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H10"/>
+  <autoFilter ref="A1:H11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -808,7 +842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1922,8 +1956,125 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2003_C</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T16:07:23.057235</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T16:30:15.965615</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1372.90838</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>22.88180633333333</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>/public1/home/stu52275901007/workspace/ghj_workspace/ModelingAgent/openclaw_experiments/evolve_exp/claude_fp8_scratch_ten_5r/cpe_evaluations/round_10/train_candidate/runs/round_10/r1p1_20261003_160723; /public1/home/stu52275901007/workspace/ghj_workspace/ModelingAgent/openclaw_experiments/evolve_exp/claude_fp8_scratch_ten_5r/cpe_evaluations/round_10/train_candidate/runs/round_10/r2p1_20261003_160723</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>run_metadata_and_directory_mtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2017_D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T16:07:23.053090</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T16:41:24.897463</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>2041.844373</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>34.03073955</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>/public1/home/stu52275901007/workspace/ghj_workspace/ModelingAgent/openclaw_experiments/evolve_exp/claude_fp8_scratch_ten_5r/cpe_evaluations/round_10/train_candidate/runs/round_10/r1p2_20261003_160723; /public1/home/stu52275901007/workspace/ghj_workspace/ModelingAgent/openclaw_experiments/evolve_exp/claude_fp8_scratch_ten_5r/cpe_evaluations/round_10/train_candidate/runs/round_10/r2p2_20261003_160723</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>run_metadata_and_directory_mtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>2024_C</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T16:07:23.055771</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T16:29:20.932958</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1317.877187</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>21.96461978333333</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>/public1/home/stu52275901007/workspace/ghj_workspace/ModelingAgent/openclaw_experiments/evolve_exp/claude_fp8_scratch_ten_5r/cpe_evaluations/round_10/train_candidate/runs/round_10/r1p3_20261003_160723; /public1/home/stu52275901007/workspace/ghj_workspace/ModelingAgent/openclaw_experiments/evolve_exp/claude_fp8_scratch_ten_5r/cpe_evaluations/round_10/train_candidate/runs/round_10/r2p3_20261003_160723</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>run_metadata_and_directory_mtime</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I28"/>
+  <autoFilter ref="A1:I31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>